--- a/resources/activity.xlsx
+++ b/resources/activity.xlsx
@@ -943,7 +943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.75" customWidth="1" style="9" min="1" max="1"/>
@@ -1260,43 +1260,33 @@
     </row>
     <row r="11" ht="16.5" customHeight="1" s="8">
       <c r="A11" s="0" t="n">
-        <v>10007</v>
-      </c>
-      <c r="B11" s="22" t="n">
-        <v>1</v>
-      </c>
+        <v>10006</v>
+      </c>
+      <c r="B11" s="22" t="n"/>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t>春节活动</t>
-        </is>
-      </c>
-      <c r="D11" s="23" t="n"/>
+          <t>冰封王座首通挑战</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>每周限挑战一次，首通可得冰魄碎片，集齐50个可合成传说戒指</t>
+        </is>
+      </c>
       <c r="E11" s="22" t="n"/>
-      <c r="F11" s="25" t="n"/>
-      <c r="G11" s="11" t="n"/>
+      <c r="F11" s="25" t="inlineStr">
+        <is>
+          <t>2025-01-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>2025-01-30 23:59:59</t>
+        </is>
+      </c>
       <c r="H11" s="11" t="n"/>
       <c r="I11" s="11" t="n"/>
       <c r="J11" s="11" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="0" t="n">
-        <v>10008</v>
-      </c>
-      <c r="B12" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>春节活动</t>
-        </is>
-      </c>
-      <c r="D12" s="23" t="n"/>
-      <c r="E12" s="22" t="n"/>
-      <c r="F12" s="25" t="n"/>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="n"/>
-      <c r="I12" s="11" t="n"/>
-      <c r="J12" s="11" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4 A8:A1048576">

--- a/resources/activity.xlsx
+++ b/resources/activity.xlsx
@@ -943,7 +943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.75" customWidth="1" style="9" min="1" max="1"/>
@@ -1288,6 +1288,38 @@
       <c r="I11" s="11" t="n"/>
       <c r="J11" s="11" t="n"/>
     </row>
+    <row r="12">
+      <c r="A12" s="0" t="n">
+        <v>10007</v>
+      </c>
+      <c r="B12" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>中秋赏月</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>中秋期间参与赏月领好礼</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="n"/>
+      <c r="F12" s="25" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>2025-10-01 23:59:59</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="n"/>
+      <c r="I12" s="11" t="n"/>
+      <c r="J12" s="11" t="n"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4 A8:A1048576">
     <cfRule type="duplicateValues" priority="11" dxfId="0"/>

--- a/resources/activity.xlsx
+++ b/resources/activity.xlsx
@@ -943,7 +943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.75" customWidth="1" style="9" min="1" max="1"/>
@@ -1320,6 +1320,24 @@
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="11" t="n"/>
     </row>
+    <row r="13">
+      <c r="A13" s="0" t="n">
+        <v>10009</v>
+      </c>
+      <c r="B13" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="22" t="n">
+        <v>10008</v>
+      </c>
+      <c r="D13" s="23" t="n"/>
+      <c r="E13" s="22" t="n"/>
+      <c r="F13" s="25" t="n"/>
+      <c r="G13" s="11" t="n"/>
+      <c r="H13" s="11" t="n"/>
+      <c r="I13" s="11" t="n"/>
+      <c r="J13" s="11" t="n"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4 A8:A1048576">
     <cfRule type="duplicateValues" priority="11" dxfId="0"/>

--- a/resources/activity.xlsx
+++ b/resources/activity.xlsx
@@ -239,9 +239,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm:ss"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="9">
     <font>
       <name val="宋体"/>
@@ -380,7 +378,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -444,18 +442,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -943,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.75" customWidth="1" style="9" min="1" max="1"/>
@@ -1083,40 +1069,40 @@
       <c r="J4" s="10" t="n"/>
     </row>
     <row r="5" ht="16.5" customHeight="1" s="8">
-      <c r="A5" s="0" t="n">
-        <v>3010</v>
-      </c>
-      <c r="B5" s="22" t="n">
+      <c r="A5" s="16" t="n">
+        <v>10001</v>
+      </c>
+      <c r="B5" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="22" t="inlineStr">
-        <is>
-          <t>冰封王座首通挑战</t>
-        </is>
-      </c>
-      <c r="D5" s="23" t="inlineStr">
-        <is>
-          <t>每周限挑战一次，首通可得冰魄碎片，集齐50个可合成传说戒指</t>
-        </is>
-      </c>
-      <c r="E5" s="22" t="n"/>
-      <c r="F5" s="25" t="inlineStr">
-        <is>
-          <t>2025-01-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>2025-01-30 23:59:59</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="n"/>
-      <c r="I5" s="11" t="n"/>
-      <c r="J5" s="11" t="n"/>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>开服活动</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>开服活动1</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="n"/>
+      <c r="F5" s="20" t="n">
+        <v>45889.41666666666</v>
+      </c>
+      <c r="G5" s="20" t="n">
+        <v>45894.41666666666</v>
+      </c>
+      <c r="H5" s="20" t="n">
+        <v>45889.41666666666</v>
+      </c>
+      <c r="I5" s="20" t="n">
+        <v>45894.41666666666</v>
+      </c>
+      <c r="J5" s="20" t="n"/>
     </row>
     <row r="6" ht="16.5" customHeight="1" s="8">
       <c r="A6" s="16" t="n">
-        <v>10001</v>
+        <v>10002</v>
       </c>
       <c r="B6" s="21" t="n">
         <v>1</v>
@@ -1128,7 +1114,7 @@
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t>开服活动1</t>
+          <t>开服活动2</t>
         </is>
       </c>
       <c r="E6" s="21" t="n"/>
@@ -1148,19 +1134,19 @@
     </row>
     <row r="7" ht="16.5" customHeight="1" s="8">
       <c r="A7" s="16" t="n">
-        <v>10002</v>
+        <v>10003</v>
       </c>
       <c r="B7" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
-          <t>开服活动</t>
+          <t>七日签到</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t>开服活动2</t>
+          <t>七日签到</t>
         </is>
       </c>
       <c r="E7" s="21" t="n"/>
@@ -1179,165 +1165,19 @@
       <c r="J7" s="20" t="n"/>
     </row>
     <row r="8" ht="16.5" customHeight="1" s="8">
-      <c r="A8" s="16" t="n">
-        <v>10003</v>
-      </c>
-      <c r="B8" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" s="21" t="inlineStr">
-        <is>
-          <t>七日签到</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>七日签到</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="n"/>
-      <c r="F8" s="20" t="n">
-        <v>45889.41666666666</v>
-      </c>
-      <c r="G8" s="20" t="n">
-        <v>45894.41666666666</v>
-      </c>
-      <c r="H8" s="20" t="n">
-        <v>45889.41666666666</v>
-      </c>
-      <c r="I8" s="20" t="n">
-        <v>45894.41666666666</v>
-      </c>
-      <c r="J8" s="20" t="n"/>
-    </row>
-    <row r="9" ht="16.5" customHeight="1" s="8">
-      <c r="A9" s="0" t="inlineStr">
-        <is>
-          <t>10004</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>TEST</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
-        <is>
-          <t>TEST</t>
-        </is>
-      </c>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t>TEST</t>
-        </is>
-      </c>
-      <c r="E9" s="22" t="n"/>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n"/>
-      <c r="I9" s="11" t="n"/>
-      <c r="J9" s="11" t="n"/>
-    </row>
-    <row r="10" ht="16.5" customHeight="1" s="8">
-      <c r="A10" s="0" t="n">
-        <v>10005</v>
-      </c>
-      <c r="B10" s="22" t="n"/>
-      <c r="C10" s="22" t="inlineStr">
-        <is>
-          <t>周年庆</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="n"/>
-      <c r="E10" s="22" t="n"/>
-      <c r="F10" s="25" t="n">
-        <v>46193</v>
-      </c>
-      <c r="G10" s="11" t="n"/>
-      <c r="H10" s="11" t="n"/>
-      <c r="I10" s="11" t="n"/>
-      <c r="J10" s="11" t="n"/>
-    </row>
-    <row r="11" ht="16.5" customHeight="1" s="8">
-      <c r="A11" s="0" t="n">
-        <v>10006</v>
-      </c>
-      <c r="B11" s="22" t="n"/>
-      <c r="C11" s="22" t="inlineStr">
-        <is>
-          <t>冰封王座首通挑战</t>
-        </is>
-      </c>
-      <c r="D11" s="23" t="inlineStr">
-        <is>
-          <t>每周限挑战一次，首通可得冰魄碎片，集齐50个可合成传说戒指</t>
-        </is>
-      </c>
-      <c r="E11" s="22" t="n"/>
-      <c r="F11" s="25" t="inlineStr">
-        <is>
-          <t>2025-01-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>2025-01-30 23:59:59</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="n"/>
-      <c r="I11" s="11" t="n"/>
-      <c r="J11" s="11" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="0" t="n">
-        <v>10007</v>
-      </c>
-      <c r="B12" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>中秋赏月</t>
-        </is>
-      </c>
-      <c r="D12" s="23" t="inlineStr">
-        <is>
-          <t>中秋期间参与赏月领好礼</t>
-        </is>
-      </c>
-      <c r="E12" s="22" t="n"/>
-      <c r="F12" s="25" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>2025-10-01 23:59:59</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="n"/>
-      <c r="I12" s="11" t="n"/>
-      <c r="J12" s="11" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="0" t="n">
-        <v>10009</v>
-      </c>
-      <c r="B13" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="22" t="n">
-        <v>10008</v>
-      </c>
-      <c r="D13" s="23" t="n"/>
-      <c r="E13" s="22" t="n"/>
-      <c r="F13" s="25" t="n"/>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="n"/>
-      <c r="I13" s="11" t="n"/>
-      <c r="J13" s="11" t="n"/>
-    </row>
+      <c r="B8" s="19" t="n"/>
+      <c r="C8" s="19" t="n"/>
+      <c r="D8" s="18" t="n"/>
+      <c r="E8" s="19" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="11" t="n"/>
+      <c r="H8" s="11" t="n"/>
+      <c r="I8" s="11" t="n"/>
+      <c r="J8" s="11" t="n"/>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" s="8"/>
+    <row r="10" ht="16.5" customHeight="1" s="8"/>
+    <row r="11" ht="16.5" customHeight="1" s="8"/>
   </sheetData>
   <conditionalFormatting sqref="A1:A4 A8:A1048576">
     <cfRule type="duplicateValues" priority="11" dxfId="0"/>

--- a/resources/activity.xlsx
+++ b/resources/activity.xlsx
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.75" customWidth="1" style="9" min="1" max="1"/>
@@ -1164,17 +1164,7 @@
       </c>
       <c r="J7" s="20" t="n"/>
     </row>
-    <row r="8" ht="16.5" customHeight="1" s="8">
-      <c r="B8" s="19" t="n"/>
-      <c r="C8" s="19" t="n"/>
-      <c r="D8" s="18" t="n"/>
-      <c r="E8" s="19" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n"/>
-      <c r="I8" s="11" t="n"/>
-      <c r="J8" s="11" t="n"/>
-    </row>
+    <row r="8" ht="16.5" customHeight="1" s="8"/>
     <row r="9" ht="16.5" customHeight="1" s="8"/>
     <row r="10" ht="16.5" customHeight="1" s="8"/>
     <row r="11" ht="16.5" customHeight="1" s="8"/>

--- a/resources/activity.xlsx
+++ b/resources/activity.xlsx
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.75" customWidth="1" style="9" min="1" max="1"/>
@@ -1164,8 +1164,62 @@
       </c>
       <c r="J7" s="20" t="n"/>
     </row>
-    <row r="8" ht="16.5" customHeight="1" s="8"/>
-    <row r="9" ht="16.5" customHeight="1" s="8"/>
+    <row r="8" ht="16.5" customHeight="1" s="8">
+      <c r="A8" s="16" t="n">
+        <v>10004</v>
+      </c>
+      <c r="B8" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>中秋签到</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="n"/>
+      <c r="E8" s="21" t="n"/>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>2025-10-01 23:59:59</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="n"/>
+      <c r="I8" s="20" t="n"/>
+      <c r="J8" s="20" t="n"/>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" s="8">
+      <c r="A9" s="16" t="n">
+        <v>11111</v>
+      </c>
+      <c r="B9" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>中秋签到</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="n"/>
+      <c r="E9" s="21" t="n"/>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>2025-10-01 23:59:59</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="n"/>
+      <c r="I9" s="20" t="n"/>
+      <c r="J9" s="20" t="n"/>
+    </row>
     <row r="10" ht="16.5" customHeight="1" s="8"/>
     <row r="11" ht="16.5" customHeight="1" s="8"/>
   </sheetData>

--- a/resources/activity.xlsx
+++ b/resources/activity.xlsx
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.75" customWidth="1" style="9" min="1" max="1"/>
@@ -1220,7 +1220,34 @@
       <c r="I9" s="20" t="n"/>
       <c r="J9" s="20" t="n"/>
     </row>
-    <row r="10" ht="16.5" customHeight="1" s="8"/>
+    <row r="10" ht="16.5" customHeight="1" s="8">
+      <c r="A10" s="16" t="n">
+        <v>11112</v>
+      </c>
+      <c r="B10" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>中秋签到</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="n"/>
+      <c r="E10" s="21" t="n"/>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>2025-10-01 23:59:59</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="n"/>
+      <c r="I10" s="20" t="n"/>
+      <c r="J10" s="20" t="n"/>
+    </row>
     <row r="11" ht="16.5" customHeight="1" s="8"/>
   </sheetData>
   <conditionalFormatting sqref="A1:A4 A8:A1048576">

--- a/resources/activity.xlsx
+++ b/resources/activity.xlsx
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.75" customWidth="1" style="9" min="1" max="1"/>
@@ -1070,39 +1070,55 @@
     </row>
     <row r="5" ht="16.5" customHeight="1" s="8">
       <c r="A5" s="16" t="n">
-        <v>10001</v>
+        <v>7001</v>
       </c>
       <c r="B5" s="21" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>开服活动</t>
+          <t>七日试炼</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>开服活动1</t>
-        </is>
-      </c>
-      <c r="E5" s="21" t="n"/>
-      <c r="F5" s="20" t="n">
-        <v>45889.41666666666</v>
-      </c>
-      <c r="G5" s="20" t="n">
-        <v>45894.41666666666</v>
-      </c>
-      <c r="H5" s="20" t="n">
-        <v>45889.41666666666</v>
-      </c>
-      <c r="I5" s="20" t="n">
-        <v>45894.41666666666</v>
-      </c>
-      <c r="J5" s="20" t="n"/>
+          <t>连续七天完成试炼领取奖励</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>icon_trial</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="J5" s="20" t="inlineStr">
+        <is>
+          <t>hero_all</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="16.5" customHeight="1" s="8">
       <c r="A6" s="16" t="n">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="B6" s="21" t="n">
         <v>1</v>
@@ -1114,7 +1130,7 @@
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t>开服活动2</t>
+          <t>开服活动1</t>
         </is>
       </c>
       <c r="E6" s="21" t="n"/>
@@ -1134,19 +1150,19 @@
     </row>
     <row r="7" ht="16.5" customHeight="1" s="8">
       <c r="A7" s="16" t="n">
-        <v>10003</v>
+        <v>10002</v>
       </c>
       <c r="B7" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
-          <t>七日签到</t>
+          <t>开服活动</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t>七日签到</t>
+          <t>开服活动2</t>
         </is>
       </c>
       <c r="E7" s="21" t="n"/>
@@ -1166,35 +1182,39 @@
     </row>
     <row r="8" ht="16.5" customHeight="1" s="8">
       <c r="A8" s="16" t="n">
-        <v>10004</v>
+        <v>10003</v>
       </c>
       <c r="B8" s="21" t="n">
         <v>2</v>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>中秋签到</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="n"/>
+          <t>七日签到</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>七日签到</t>
+        </is>
+      </c>
       <c r="E8" s="21" t="n"/>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="G8" s="20" t="inlineStr">
-        <is>
-          <t>2025-10-01 23:59:59</t>
-        </is>
-      </c>
-      <c r="H8" s="20" t="n"/>
-      <c r="I8" s="20" t="n"/>
+      <c r="F8" s="20" t="n">
+        <v>45889.41666666666</v>
+      </c>
+      <c r="G8" s="20" t="n">
+        <v>45894.41666666666</v>
+      </c>
+      <c r="H8" s="20" t="n">
+        <v>45889.41666666666</v>
+      </c>
+      <c r="I8" s="20" t="n">
+        <v>45894.41666666666</v>
+      </c>
       <c r="J8" s="20" t="n"/>
     </row>
     <row r="9" ht="16.5" customHeight="1" s="8">
       <c r="A9" s="16" t="n">
-        <v>11111</v>
+        <v>10004</v>
       </c>
       <c r="B9" s="21" t="n">
         <v>2</v>
@@ -1222,10 +1242,10 @@
     </row>
     <row r="10" ht="16.5" customHeight="1" s="8">
       <c r="A10" s="16" t="n">
-        <v>11112</v>
+        <v>10005</v>
       </c>
       <c r="B10" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
@@ -1248,7 +1268,162 @@
       <c r="I10" s="20" t="n"/>
       <c r="J10" s="20" t="n"/>
     </row>
-    <row r="11" ht="16.5" customHeight="1" s="8"/>
+    <row r="11" ht="16.5" customHeight="1" s="8">
+      <c r="A11" s="16" t="n">
+        <v>10006</v>
+      </c>
+      <c r="B11" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>春节活动</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="n"/>
+      <c r="E11" s="21" t="n"/>
+      <c r="F11" s="20" t="n"/>
+      <c r="G11" s="20" t="n"/>
+      <c r="H11" s="20" t="n"/>
+      <c r="I11" s="20" t="n"/>
+      <c r="J11" s="20" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="n">
+        <v>10007</v>
+      </c>
+      <c r="B12" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>春节活动</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="n"/>
+      <c r="E12" s="21" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="20" t="n"/>
+      <c r="H12" s="20" t="n"/>
+      <c r="I12" s="20" t="n"/>
+      <c r="J12" s="20" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="n">
+        <v>10008</v>
+      </c>
+      <c r="B13" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>春节活动</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="n"/>
+      <c r="E13" s="21" t="n"/>
+      <c r="F13" s="20" t="n"/>
+      <c r="G13" s="20" t="n"/>
+      <c r="H13" s="20" t="n"/>
+      <c r="I13" s="20" t="n"/>
+      <c r="J13" s="20" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="n">
+        <v>10009</v>
+      </c>
+      <c r="B14" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>中秋签到</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="n"/>
+      <c r="E14" s="21" t="n"/>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>2025-10-01 23:59:59</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="n"/>
+      <c r="I14" s="20" t="n"/>
+      <c r="J14" s="20" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="n">
+        <v>10010</v>
+      </c>
+      <c r="B15" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>开服庆典</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="n"/>
+      <c r="E15" s="21" t="n"/>
+      <c r="F15" s="20" t="n"/>
+      <c r="G15" s="20" t="n"/>
+      <c r="H15" s="20" t="n"/>
+      <c r="I15" s="20" t="n"/>
+      <c r="J15" s="20" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="n">
+        <v>10011</v>
+      </c>
+      <c r="B16" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>春节活动</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="n"/>
+      <c r="E16" s="21" t="n"/>
+      <c r="F16" s="20" t="n"/>
+      <c r="G16" s="20" t="n"/>
+      <c r="H16" s="20" t="n"/>
+      <c r="I16" s="20" t="n"/>
+      <c r="J16" s="20" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="n">
+        <v>10012</v>
+      </c>
+      <c r="B17" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>中秋签到</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="n"/>
+      <c r="E17" s="21" t="n"/>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>2025-10-01 23:59:59</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="n"/>
+      <c r="I17" s="20" t="n"/>
+      <c r="J17" s="20" t="n"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4 A8:A1048576">
     <cfRule type="duplicateValues" priority="11" dxfId="0"/>

--- a/resources/activity.xlsx
+++ b/resources/activity.xlsx
@@ -929,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.75" customWidth="1" style="9" min="1" max="1"/>
@@ -1070,55 +1070,39 @@
     </row>
     <row r="5" ht="16.5" customHeight="1" s="8">
       <c r="A5" s="16" t="n">
-        <v>7001</v>
+        <v>10001</v>
       </c>
       <c r="B5" s="21" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>七日试炼</t>
+          <t>开服活动</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>连续七天完成试炼领取奖励</t>
-        </is>
-      </c>
-      <c r="E5" s="21" t="inlineStr">
-        <is>
-          <t>icon_trial</t>
-        </is>
-      </c>
-      <c r="F5" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="G5" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="H5" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="I5" s="20" t="inlineStr">
-        <is>
-          <t>2026-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="J5" s="20" t="inlineStr">
-        <is>
-          <t>hero_all</t>
-        </is>
-      </c>
+          <t>开服活动1</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="n"/>
+      <c r="F5" s="20" t="n">
+        <v>45889.41666666666</v>
+      </c>
+      <c r="G5" s="20" t="n">
+        <v>45894.41666666666</v>
+      </c>
+      <c r="H5" s="20" t="n">
+        <v>45889.41666666666</v>
+      </c>
+      <c r="I5" s="20" t="n">
+        <v>45894.41666666666</v>
+      </c>
+      <c r="J5" s="20" t="n"/>
     </row>
     <row r="6" ht="16.5" customHeight="1" s="8">
       <c r="A6" s="16" t="n">
-        <v>10001</v>
+        <v>10002</v>
       </c>
       <c r="B6" s="21" t="n">
         <v>1</v>
@@ -1130,7 +1114,7 @@
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t>开服活动1</t>
+          <t>开服活动2</t>
         </is>
       </c>
       <c r="E6" s="21" t="n"/>
@@ -1150,19 +1134,19 @@
     </row>
     <row r="7" ht="16.5" customHeight="1" s="8">
       <c r="A7" s="16" t="n">
-        <v>10002</v>
+        <v>10003</v>
       </c>
       <c r="B7" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
-          <t>开服活动</t>
+          <t>七日签到</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t>开服活动2</t>
+          <t>七日签到</t>
         </is>
       </c>
       <c r="E7" s="21" t="n"/>
@@ -1182,248 +1166,56 @@
     </row>
     <row r="8" ht="16.5" customHeight="1" s="8">
       <c r="A8" s="16" t="n">
-        <v>10003</v>
+        <v>10004</v>
       </c>
       <c r="B8" s="21" t="n">
         <v>2</v>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>七日签到</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>七日签到</t>
-        </is>
-      </c>
+          <t>春节活动</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="n"/>
       <c r="E8" s="21" t="n"/>
-      <c r="F8" s="20" t="n">
-        <v>45889.41666666666</v>
-      </c>
-      <c r="G8" s="20" t="n">
-        <v>45894.41666666666</v>
-      </c>
-      <c r="H8" s="20" t="n">
-        <v>45889.41666666666</v>
-      </c>
-      <c r="I8" s="20" t="n">
-        <v>45894.41666666666</v>
-      </c>
+      <c r="F8" s="20" t="n"/>
+      <c r="G8" s="20" t="n"/>
+      <c r="H8" s="20" t="n"/>
+      <c r="I8" s="20" t="n"/>
       <c r="J8" s="20" t="n"/>
     </row>
     <row r="9" ht="16.5" customHeight="1" s="8">
       <c r="A9" s="16" t="n">
-        <v>10004</v>
+        <v>10005</v>
       </c>
       <c r="B9" s="21" t="n">
         <v>2</v>
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
-          <t>中秋签到</t>
+          <t>春节活动</t>
         </is>
       </c>
       <c r="D9" s="21" t="n"/>
       <c r="E9" s="21" t="n"/>
-      <c r="F9" s="20" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="G9" s="20" t="inlineStr">
-        <is>
-          <t>2025-10-01 23:59:59</t>
-        </is>
-      </c>
+      <c r="F9" s="20" t="n"/>
+      <c r="G9" s="20" t="n"/>
       <c r="H9" s="20" t="n"/>
       <c r="I9" s="20" t="n"/>
       <c r="J9" s="20" t="n"/>
     </row>
     <row r="10" ht="16.5" customHeight="1" s="8">
-      <c r="A10" s="16" t="n">
-        <v>10005</v>
-      </c>
-      <c r="B10" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>中秋签到</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="n"/>
-      <c r="E10" s="21" t="n"/>
-      <c r="F10" s="20" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="G10" s="20" t="inlineStr">
-        <is>
-          <t>2025-10-01 23:59:59</t>
-        </is>
-      </c>
-      <c r="H10" s="20" t="n"/>
-      <c r="I10" s="20" t="n"/>
-      <c r="J10" s="20" t="n"/>
-    </row>
-    <row r="11" ht="16.5" customHeight="1" s="8">
-      <c r="A11" s="16" t="n">
-        <v>10006</v>
-      </c>
-      <c r="B11" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" s="21" t="inlineStr">
-        <is>
-          <t>春节活动</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="n"/>
-      <c r="E11" s="21" t="n"/>
-      <c r="F11" s="20" t="n"/>
-      <c r="G11" s="20" t="n"/>
-      <c r="H11" s="20" t="n"/>
-      <c r="I11" s="20" t="n"/>
-      <c r="J11" s="20" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="n">
-        <v>10007</v>
-      </c>
-      <c r="B12" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" s="21" t="inlineStr">
-        <is>
-          <t>春节活动</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="n"/>
-      <c r="E12" s="21" t="n"/>
-      <c r="F12" s="20" t="n"/>
-      <c r="G12" s="20" t="n"/>
-      <c r="H12" s="20" t="n"/>
-      <c r="I12" s="20" t="n"/>
-      <c r="J12" s="20" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="16" t="n">
-        <v>10008</v>
-      </c>
-      <c r="B13" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" s="21" t="inlineStr">
-        <is>
-          <t>春节活动</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="n"/>
-      <c r="E13" s="21" t="n"/>
-      <c r="F13" s="20" t="n"/>
-      <c r="G13" s="20" t="n"/>
-      <c r="H13" s="20" t="n"/>
-      <c r="I13" s="20" t="n"/>
-      <c r="J13" s="20" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="16" t="n">
-        <v>10009</v>
-      </c>
-      <c r="B14" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C14" s="21" t="inlineStr">
-        <is>
-          <t>中秋签到</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="n"/>
-      <c r="E14" s="21" t="n"/>
-      <c r="F14" s="20" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="G14" s="20" t="inlineStr">
-        <is>
-          <t>2025-10-01 23:59:59</t>
-        </is>
-      </c>
-      <c r="H14" s="20" t="n"/>
-      <c r="I14" s="20" t="n"/>
-      <c r="J14" s="20" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="n">
-        <v>10010</v>
-      </c>
-      <c r="B15" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
-        <is>
-          <t>开服庆典</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="n"/>
-      <c r="E15" s="21" t="n"/>
-      <c r="F15" s="20" t="n"/>
-      <c r="G15" s="20" t="n"/>
-      <c r="H15" s="20" t="n"/>
-      <c r="I15" s="20" t="n"/>
-      <c r="J15" s="20" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="16" t="n">
-        <v>10011</v>
-      </c>
-      <c r="B16" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>春节活动</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="n"/>
-      <c r="E16" s="21" t="n"/>
-      <c r="F16" s="20" t="n"/>
-      <c r="G16" s="20" t="n"/>
-      <c r="H16" s="20" t="n"/>
-      <c r="I16" s="20" t="n"/>
-      <c r="J16" s="20" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="16" t="n">
-        <v>10012</v>
-      </c>
-      <c r="B17" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
-        <is>
-          <t>中秋签到</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="n"/>
-      <c r="E17" s="21" t="n"/>
-      <c r="F17" s="20" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="G17" s="20" t="inlineStr">
-        <is>
-          <t>2025-10-01 23:59:59</t>
-        </is>
-      </c>
-      <c r="H17" s="20" t="n"/>
-      <c r="I17" s="20" t="n"/>
-      <c r="J17" s="20" t="n"/>
-    </row>
+      <c r="B10" s="19" t="n"/>
+      <c r="C10" s="19" t="n"/>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="11" t="n"/>
+      <c r="G10" s="11" t="n"/>
+      <c r="H10" s="11" t="n"/>
+      <c r="I10" s="11" t="n"/>
+      <c r="J10" s="11" t="n"/>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" s="8"/>
   </sheetData>
   <conditionalFormatting sqref="A1:A4 A8:A1048576">
     <cfRule type="duplicateValues" priority="11" dxfId="0"/>
